--- a/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_3.xlsx
+++ b/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethylene/bio_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F76043F-2C00-2847-B590-5A6BD251C4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2AC43B-E677-DC48-8EBC-DDCE9BA170F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1014,8 +1014,8 @@
     <col min="106" max="106" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="107" max="107" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="108" max="108" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="109" max="127" width="10.83203125" style="1" customWidth="1"/>
-    <col min="128" max="16384" width="10.83203125" style="1"/>
+    <col min="109" max="126" width="10.83203125" style="1" customWidth="1"/>
+    <col min="127" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:108" x14ac:dyDescent="0.2">
